--- a/input/site_data.xlsx
+++ b/input/site_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://atea-my.sharepoint.com/personal/umair_ali_syed_atea_dk/Documents/ScriptAtea/yml-generator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{D8734FDA-1D9A-7E48-8A97-349C80A6FD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5D9F8B7-7FFE-864C-9061-E3D9A2D25047}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{D8734FDA-1D9A-7E48-8A97-349C80A6FD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3754F14-08DC-E248-BD7F-63436FE6DF5D}"/>
   <bookViews>
-    <workbookView xWindow="10480" yWindow="600" windowWidth="30240" windowHeight="17460" xr2:uid="{20CEB49C-714A-8F4A-8D19-BC681C3D5233}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17460" xr2:uid="{20CEB49C-714A-8F4A-8D19-BC681C3D5233}"/>
   </bookViews>
   <sheets>
     <sheet name="MACAddress" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>vlan_id</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>devID</t>
+  </si>
+  <si>
+    <t>111.111.111</t>
   </si>
 </sst>
 </file>
@@ -483,8 +486,8 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
-        <v>100</v>
+      <c r="A2" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>

--- a/input/site_data.xlsx
+++ b/input/site_data.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://atea-my.sharepoint.com/personal/umair_ali_syed_atea_dk/Documents/ScriptAtea/yml-generator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{D8734FDA-1D9A-7E48-8A97-349C80A6FD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3754F14-08DC-E248-BD7F-63436FE6DF5D}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{D8734FDA-1D9A-7E48-8A97-349C80A6FD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53D90AAE-8951-A240-9B16-C28BB481C967}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17460" xr2:uid="{20CEB49C-714A-8F4A-8D19-BC681C3D5233}"/>
   </bookViews>
   <sheets>
-    <sheet name="MACAddress" sheetId="2" r:id="rId1"/>
+    <sheet name="mac_addresses" sheetId="2" r:id="rId1"/>
     <sheet name="vlans" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>vlan_id</t>
   </si>
@@ -81,26 +81,37 @@
     <t>10.30.30.1</t>
   </si>
   <si>
-    <t>mac</t>
-  </si>
-  <si>
-    <t>devID</t>
-  </si>
-  <si>
     <t>111.111.111</t>
+  </si>
+  <si>
+    <t>device_name</t>
+  </si>
+  <si>
+    <t>mac_address</t>
+  </si>
+  <si>
+    <t>aa:bb:cc:dd:ee:02</t>
+  </si>
+  <si>
+    <t>aa:bb:cc:dd:ee:03</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
     </font>
     <font>
       <b/>
@@ -134,10 +145,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,17 +489,17 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
@@ -495,9 +507,9 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>200</v>
+    <row r="3" spans="1:4" ht="21" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
@@ -505,9 +517,9 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>300</v>
+    <row r="4" spans="1:4" ht="21" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>

--- a/input/site_data.xlsx
+++ b/input/site_data.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://atea-my.sharepoint.com/personal/umair_ali_syed_atea_dk/Documents/ScriptAtea/yml-generator/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{D8734FDA-1D9A-7E48-8A97-349C80A6FD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53D90AAE-8951-A240-9B16-C28BB481C967}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{D8734FDA-1D9A-7E48-8A97-349C80A6FD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87188DA7-DBB0-4948-ABAF-4EEC92F0CA79}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17460" xr2:uid="{20CEB49C-714A-8F4A-8D19-BC681C3D5233}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17460" activeTab="1" xr2:uid="{20CEB49C-714A-8F4A-8D19-BC681C3D5233}"/>
   </bookViews>
   <sheets>
     <sheet name="mac_addresses" sheetId="2" r:id="rId1"/>
-    <sheet name="vlans" sheetId="1" r:id="rId2"/>
+    <sheet name="site_info" sheetId="3" r:id="rId2"/>
+    <sheet name="vlans" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>vlan_id</t>
   </si>
@@ -94,6 +95,15 @@
   </si>
   <si>
     <t>aa:bb:cc:dd:ee:03</t>
+  </si>
+  <si>
+    <t>site_name</t>
+  </si>
+  <si>
+    <t>site_id</t>
+  </si>
+  <si>
+    <t>segev</t>
   </si>
 </sst>
 </file>
@@ -489,12 +499,11 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -536,6 +545,32 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04C5B047-1B92-4541-8693-EAADCFCB32FD}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89414C40-3D16-CA42-B60B-9A6812F56FC4}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
